--- a/data/trans_dic/IP13_R1_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R1_2023-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor</t>
+          <t>Menores que limitaron su actividad por dolor (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 10,53</t>
+          <t>1,14; 10,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,18</t>
+          <t>0,56; 4,82</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,97</t>
+          <t>0,31; 4,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,02</t>
+          <t>0,71; 4,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,13</t>
+          <t>0,79; 2,96</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,66</t>
+          <t>0,41; 3,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,02</t>
+          <t>0,91; 5,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,45</t>
+          <t>0,89; 3,41</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,14</t>
+          <t>0,45; 3,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,8</t>
+          <t>0,29; 3,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,39</t>
+          <t>0,59; 2,33</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,68</t>
+          <t>0,89; 2,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,57</t>
+          <t>0,9; 2,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,26</t>
+          <t>1,03; 2,17</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que limitaron su actividad por dolor (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2441</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2441</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>655; 6059</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>668; 5735</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2064</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3355</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5419</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>494; 6403</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1283; 7441</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2702; 10102</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2346</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4964</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7310</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>717; 5864</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1934; 10709</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3435; 13160</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3729</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3544</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7274</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1238; 8506</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>876; 9177</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3424; 13528</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>10579</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>11864</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>22443</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>5914; 16840</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6848; 19006</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>14731; 31003</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP13_R1_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R1_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor (tasa de respuesta: 99,95%)</t>
+          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 10,53</t>
+          <t>1,14; 9,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,82</t>
+          <t>0,56; 5,04</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,02</t>
+          <t>0,32; 3,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,09</t>
+          <t>0,76; 4,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,96</t>
+          <t>0,74; 3,07</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,39</t>
+          <t>0,27; 3,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,04</t>
+          <t>0,95; 4,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,41</t>
+          <t>0,95; 3,72</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,09</t>
+          <t>0,45; 3,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,0</t>
+          <t>0,29; 2,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,33</t>
+          <t>0,63; 2,43</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,53</t>
+          <t>0,9; 2,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,5</t>
+          <t>0,89; 2,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,17</t>
+          <t>1,09; 2,22</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor (tasa de respuesta: 99,95%)</t>
+          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,7 +930,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>655; 6059</t>
+          <t>657; 5577</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>668; 5735</t>
+          <t>666; 5993</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>494; 6403</t>
+          <t>506; 6245</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1283; 7441</t>
+          <t>1387; 7735</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2702; 10102</t>
+          <t>2530; 10461</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>717; 5864</t>
+          <t>470; 6295</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1934; 10709</t>
+          <t>2016; 10460</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3435; 13160</t>
+          <t>3650; 14337</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1238; 8506</t>
+          <t>1248; 8555</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>876; 9177</t>
+          <t>879; 8384</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3424; 13528</t>
+          <t>3650; 14110</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5914; 16840</t>
+          <t>5973; 16943</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6848; 19006</t>
+          <t>6812; 19822</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14731; 31003</t>
+          <t>15480; 31705</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP13_R1_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R1_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 9,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,28; 10,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,04</t>
+          <t>0,49; 5,28</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,92</t>
+          <t>0,62; 4,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,25</t>
+          <t>0,29; 4,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,07</t>
+          <t>0,73; 3,3</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,64</t>
+          <t>0,95; 5,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,92</t>
+          <t>0,4; 3,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,72</t>
+          <t>0,97; 3,53</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,11</t>
+          <t>0,31; 2,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,74</t>
+          <t>0,53; 3,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,43</t>
+          <t>0,59; 2,64</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,55</t>
+          <t>0,92; 2,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,6</t>
+          <t>0,99; 2,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,22</t>
+          <t>1,12; 2,38</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2170</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>2170</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>657; 5577</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>668; 5328</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>666; 5993</t>
+          <t>504; 5418</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2786</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>2064</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3355</t>
-        </is>
-      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>4850</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>506; 6245</t>
+          <t>971; 6351</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1387; 7735</t>
+          <t>423; 6468</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2530; 10461</t>
+          <t>2195; 9968</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>4973</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>2281</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>7254</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>470; 6295</t>
+          <t>1897; 10632</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2016; 10460</t>
+          <t>694; 6107</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3650; 14337</t>
+          <t>3644; 13220</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7274</t>
+          <t>7662</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1248; 8555</t>
+          <t>902; 8705</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>879; 8384</t>
+          <t>1372; 9259</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3650; 14110</t>
+          <t>3232; 14476</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10579</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>21936</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5973; 16943</t>
+          <t>6463; 19047</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6812; 19822</t>
+          <t>6234; 17946</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15480; 31705</t>
+          <t>14947; 31695</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP13_R1_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R1_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor (tasa de respuesta: 99,95%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,28; 10,23</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,49; 5,28</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,62; 4,05</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,29; 4,45</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,73; 3,3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,95; 5,31</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,4; 3,5</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,97; 3,53</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,31; 2,97</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,53; 3,61</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,59; 2,64</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,92; 2,72</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,99; 2,85</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1,12; 2,38</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,47 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.04165750333188268</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.02114375237799076</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2170</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2170</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="n">
+        <v>0.01282959915712103</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.004907470955143483</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>668; 5328</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>504; 5418</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>0.1022840702375229</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.05278915498925922</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +603,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.01774965265482583</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.01418196242916269</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.01603342938237983</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2786</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2064</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4850</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.006187431586093741</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.002906629171143631</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.007255410377016886</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>971; 6351</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>423; 6468</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2195; 9968</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.04045735141438895</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.04445008762769751</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.0329511802529914</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +658,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.0248485821982517</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.01305807127618781</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.01935368944513718</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>4973</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2281</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7254</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.009476791078892315</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.003973892222961479</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.009723881858724834</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1897; 10632</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>694; 6107</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3644; 13220</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.05312796949708503</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.03496402906681664</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.03527194484268389</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +713,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.0124349850420373</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.01568100561720099</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.01395133689635444</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>3639</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>4023</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>7662</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.00308149628460598</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.005346170025278684</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.005884173823706348</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>902; 8705</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>1372; 9259</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>3232; 14476</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.02974577390201929</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.0360892035132862</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.02635859697224657</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +768,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.01627647939490868</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.01675730457722871</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.01650396627336009</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>11398</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>10538</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>21936</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.009228946470148621</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.009913507837601931</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.01124559150521213</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>6463; 19047</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>6234; 17946</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>14947; 31695</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.02719846505330167</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.02853823238181116</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.02384663201447618</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +833,445 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>2170</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="6" t="n">
+        <v>668</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="n">
+        <v>5328</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>5418</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>2786</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>2064</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>4850</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>971</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>423</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>6351</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>6468</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>9968</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>4973</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>2281</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>7254</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>1897</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>694</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>3644</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>10632</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>6107</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>13220</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>3639</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>4023</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>7662</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>902</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>1372</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>3232</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>8705</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>9259</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>14476</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>11398</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>10538</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>21936</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>6463</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>6234</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>14947</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>19047</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>17946</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>31695</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>